--- a/output/yearly_benthic_cover_iteration_1_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_1_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.09041885007282</v>
+        <v>44.78364146049694</v>
       </c>
       <c r="M2" t="n">
-        <v>100.7030085049109</v>
+        <v>100.7156374904775</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.10258400506625</v>
+        <v>87.9272438650878</v>
       </c>
       <c r="C3" t="n">
-        <v>45.95092709018155</v>
+        <v>45.81881193808258</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228906706926028</v>
+        <v>2.228557072459005</v>
       </c>
       <c r="E3" t="n">
-        <v>5.723214922015766</v>
+        <v>5.638374198469602</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429689023086761</v>
+        <v>0.742852357486335</v>
       </c>
       <c r="G3" t="n">
-        <v>33.98004679407227</v>
+        <v>33.93598195336965</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17656950619909</v>
+        <v>34.17120844437141</v>
       </c>
       <c r="I3" t="n">
-        <v>6.607321534115191</v>
+        <v>6.567442604642203</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643555639429225</v>
+        <v>4.642827234289594</v>
       </c>
       <c r="K3" t="n">
-        <v>11.89741599493373</v>
+        <v>12.07275613491221</v>
       </c>
       <c r="L3" t="n">
-        <v>48.91450669182392</v>
+        <v>48.87267605839214</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7628497769392</v>
+        <v>106.7642441313869</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.22721204701445</v>
+        <v>86.9401045826849</v>
       </c>
       <c r="C4" t="n">
-        <v>42.71744891367581</v>
+        <v>42.470771105582</v>
       </c>
       <c r="D4" t="n">
-        <v>2.186977931313207</v>
+        <v>2.180507065434758</v>
       </c>
       <c r="E4" t="n">
-        <v>6.535171978424962</v>
+        <v>6.430867800668595</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445354959399624</v>
+        <v>0.7444143839348336</v>
       </c>
       <c r="G4" t="n">
-        <v>33.34083576163443</v>
+        <v>33.20428690665725</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24863281323827</v>
+        <v>34.24306166100234</v>
       </c>
       <c r="I4" t="n">
-        <v>5.517711216838863</v>
+        <v>5.48437686539441</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653346849624765</v>
+        <v>4.65258989959271</v>
       </c>
       <c r="K4" t="n">
-        <v>12.77278795298556</v>
+        <v>13.0598954173151</v>
       </c>
       <c r="L4" t="n">
-        <v>44.32622642405764</v>
+        <v>44.28690451586284</v>
       </c>
       <c r="M4" t="n">
-        <v>99.816463290719</v>
+        <v>99.81757103875994</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.139435358566</v>
+        <v>85.75215120938769</v>
       </c>
       <c r="C5" t="n">
-        <v>42.48609325898065</v>
+        <v>42.13384179248078</v>
       </c>
       <c r="D5" t="n">
-        <v>2.134218693872711</v>
+        <v>2.122330849158962</v>
       </c>
       <c r="E5" t="n">
-        <v>7.145230542605377</v>
+        <v>7.022366055679306</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458626254033328</v>
+        <v>0.7457392340812312</v>
       </c>
       <c r="G5" t="n">
-        <v>32.53651256969606</v>
+        <v>32.31839214988877</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30968076855331</v>
+        <v>34.30400476773663</v>
       </c>
       <c r="I5" t="n">
-        <v>4.606288749664387</v>
+        <v>4.578447939835085</v>
       </c>
       <c r="J5" t="n">
-        <v>4.66164140877083</v>
+        <v>4.660870213007694</v>
       </c>
       <c r="K5" t="n">
-        <v>13.86056464143399</v>
+        <v>14.24784879061232</v>
       </c>
       <c r="L5" t="n">
-        <v>43.50007234356209</v>
+        <v>43.4659656150904</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84673024397674</v>
+        <v>99.8476561981835</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.81073785533823</v>
+        <v>84.39341054064634</v>
       </c>
       <c r="C6" t="n">
-        <v>41.87288925469197</v>
+        <v>41.48598316726624</v>
       </c>
       <c r="D6" t="n">
-        <v>2.069526391884454</v>
+        <v>2.055880479858517</v>
       </c>
       <c r="E6" t="n">
-        <v>7.569373749436512</v>
+        <v>7.43935041925192</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469895954390062</v>
+        <v>0.7468647436721313</v>
       </c>
       <c r="G6" t="n">
-        <v>31.55026785970149</v>
+        <v>31.30650039210381</v>
       </c>
       <c r="H6" t="n">
-        <v>34.36152139019428</v>
+        <v>34.35577820891803</v>
       </c>
       <c r="I6" t="n">
-        <v>3.844373897188699</v>
+        <v>3.821131648891108</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668684971493789</v>
+        <v>4.667904647950819</v>
       </c>
       <c r="K6" t="n">
-        <v>15.18926214466178</v>
+        <v>15.60658945935367</v>
       </c>
       <c r="L6" t="n">
-        <v>42.8098961353778</v>
+        <v>42.78024826394022</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87204753473154</v>
+        <v>99.87282089056013</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.24477933211286</v>
+        <v>82.8748128234304</v>
       </c>
       <c r="C7" t="n">
-        <v>40.90413989229006</v>
+        <v>40.56071104668311</v>
       </c>
       <c r="D7" t="n">
-        <v>1.993402873158387</v>
+        <v>1.981901095884731</v>
       </c>
       <c r="E7" t="n">
-        <v>7.825575650759058</v>
+        <v>7.703044047183726</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479490803406947</v>
+        <v>0.7478225230468343</v>
       </c>
       <c r="G7" t="n">
-        <v>30.38975238348016</v>
+        <v>30.1799584379031</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40565769567196</v>
+        <v>34.39983606015437</v>
       </c>
       <c r="I7" t="n">
-        <v>3.207759896573245</v>
+        <v>3.188359890214935</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674681752129342</v>
+        <v>4.673890769042713</v>
       </c>
       <c r="K7" t="n">
-        <v>16.75522066788716</v>
+        <v>17.1251871765696</v>
       </c>
       <c r="L7" t="n">
-        <v>42.23385127601199</v>
+        <v>42.20795923094477</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89321183618921</v>
+        <v>99.89385745419747</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.8930819686101</v>
+        <v>87.65354761351871</v>
       </c>
       <c r="C8" t="n">
-        <v>43.13029924190141</v>
+        <v>42.83978446739091</v>
       </c>
       <c r="D8" t="n">
-        <v>1.997568884873532</v>
+        <v>1.986096596755063</v>
       </c>
       <c r="E8" t="n">
-        <v>9.600184434492665</v>
+        <v>9.516456626220377</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7495122187674464</v>
+        <v>0.7494055939946287</v>
       </c>
       <c r="G8" t="n">
-        <v>30.87317169561021</v>
+        <v>30.67851350229749</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47756206330254</v>
+        <v>34.47265732375291</v>
       </c>
       <c r="I8" t="n">
-        <v>5.510631304267169</v>
+        <v>5.566633008031797</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684451367296541</v>
+        <v>4.683784962466428</v>
       </c>
       <c r="K8" t="n">
-        <v>12.1069180313899</v>
+        <v>12.3464523864813</v>
       </c>
       <c r="L8" t="n">
-        <v>44.57947810480846</v>
+        <v>44.62860068429132</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81669537809977</v>
+        <v>99.81483753816353</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.81600069379151</v>
+        <v>85.64733739462436</v>
       </c>
       <c r="C9" t="n">
-        <v>41.90872141785125</v>
+        <v>41.69740557371095</v>
       </c>
       <c r="D9" t="n">
-        <v>1.903270797579621</v>
+        <v>1.895055492837601</v>
       </c>
       <c r="E9" t="n">
-        <v>9.913727148952459</v>
+        <v>9.85477158895665</v>
       </c>
       <c r="F9" t="n">
-        <v>0.750851539706728</v>
+        <v>0.7507610266454134</v>
       </c>
       <c r="G9" t="n">
-        <v>29.41575960752752</v>
+        <v>29.27223460309429</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53917082650949</v>
+        <v>34.53500722568901</v>
       </c>
       <c r="I9" t="n">
-        <v>4.600398650348649</v>
+        <v>4.647251040867544</v>
       </c>
       <c r="J9" t="n">
-        <v>4.69282212316705</v>
+        <v>4.692256416533833</v>
       </c>
       <c r="K9" t="n">
-        <v>14.1839993062085</v>
+        <v>14.35266260537566</v>
       </c>
       <c r="L9" t="n">
-        <v>43.75420618415504</v>
+        <v>43.79530312624583</v>
       </c>
       <c r="M9" t="n">
-        <v>99.8469269082148</v>
+        <v>99.84537130533245</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.50435773396735</v>
+        <v>83.45361185039474</v>
       </c>
       <c r="C10" t="n">
-        <v>40.31091039093506</v>
+        <v>40.22454870075819</v>
       </c>
       <c r="D10" t="n">
-        <v>1.79932077149524</v>
+        <v>1.796493037014052</v>
       </c>
       <c r="E10" t="n">
-        <v>10.01219742798791</v>
+        <v>9.988673193951941</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520023481066885</v>
+        <v>0.7519241412890455</v>
       </c>
       <c r="G10" t="n">
-        <v>27.80917320774515</v>
+        <v>27.74977611001665</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59210801290767</v>
+        <v>34.58851049929609</v>
       </c>
       <c r="I10" t="n">
-        <v>3.839541290057886</v>
+        <v>3.878708985770422</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700014675666804</v>
+        <v>4.699525883056533</v>
       </c>
       <c r="K10" t="n">
-        <v>16.49564226603263</v>
+        <v>16.54638814960526</v>
       </c>
       <c r="L10" t="n">
-        <v>43.06565849163375</v>
+        <v>43.0999728429458</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87221114860145</v>
+        <v>99.87090969330924</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.17913242784827</v>
+        <v>80.99213201522286</v>
       </c>
       <c r="C11" t="n">
-        <v>38.58073807283506</v>
+        <v>38.3640962284568</v>
       </c>
       <c r="D11" t="n">
-        <v>1.695951928406127</v>
+        <v>1.686885845092572</v>
       </c>
       <c r="E11" t="n">
-        <v>9.970979727173061</v>
+        <v>9.918673887002441</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529916357577875</v>
+        <v>0.7529257405812464</v>
       </c>
       <c r="G11" t="n">
-        <v>26.21156920778656</v>
+        <v>26.05671358586455</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63761524485822</v>
+        <v>34.63458406673733</v>
       </c>
       <c r="I11" t="n">
-        <v>3.203826960380359</v>
+        <v>3.236563011311928</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706197723486173</v>
+        <v>4.705785878632789</v>
       </c>
       <c r="K11" t="n">
-        <v>18.82086757215171</v>
+        <v>19.00786798477715</v>
       </c>
       <c r="L11" t="n">
-        <v>42.49174043028938</v>
+        <v>42.52029387049464</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89334607527616</v>
+        <v>99.89225808372859</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.81507437679069</v>
+        <v>78.56341349043589</v>
       </c>
       <c r="C12" t="n">
-        <v>36.71241041478542</v>
+        <v>36.43600317421384</v>
       </c>
       <c r="D12" t="n">
-        <v>1.591902365608606</v>
+        <v>1.57991200014272</v>
       </c>
       <c r="E12" t="n">
-        <v>9.80472198632992</v>
+        <v>9.739718949266566</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538428484296957</v>
+        <v>0.7537883429331784</v>
       </c>
       <c r="G12" t="n">
-        <v>24.60344443100099</v>
+        <v>24.40432741690952</v>
       </c>
       <c r="H12" t="n">
-        <v>34.676771027766</v>
+        <v>34.6742637749262</v>
       </c>
       <c r="I12" t="n">
-        <v>2.672873914969873</v>
+        <v>2.700225862925341</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711517802685599</v>
+        <v>4.711177143332364</v>
       </c>
       <c r="K12" t="n">
-        <v>21.18492562320931</v>
+        <v>21.43658650956411</v>
       </c>
       <c r="L12" t="n">
-        <v>42.01366876866136</v>
+        <v>42.03750578813006</v>
       </c>
       <c r="M12" t="n">
-        <v>99.91100480665609</v>
+        <v>99.91009547190801</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.47181370367302</v>
+        <v>76.11258644056767</v>
       </c>
       <c r="C13" t="n">
-        <v>34.78188344644181</v>
+        <v>34.4019510292345</v>
       </c>
       <c r="D13" t="n">
-        <v>1.489731104648372</v>
+        <v>1.472974370169063</v>
       </c>
       <c r="E13" t="n">
-        <v>9.54702992245679</v>
+        <v>9.455879457476449</v>
       </c>
       <c r="F13" t="n">
-        <v>0.754575465884836</v>
+        <v>0.7545319075605861</v>
       </c>
       <c r="G13" t="n">
-        <v>23.02434950923463</v>
+        <v>22.75250064755166</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71047143070246</v>
+        <v>34.70846774778695</v>
       </c>
       <c r="I13" t="n">
-        <v>2.229559608965717</v>
+        <v>2.252407887769297</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716096661780226</v>
+        <v>4.715824422253662</v>
       </c>
       <c r="K13" t="n">
-        <v>23.52818629632697</v>
+        <v>23.88741355943234</v>
       </c>
       <c r="L13" t="n">
-        <v>41.61568375959316</v>
+        <v>41.63562913736302</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92575350236194</v>
+        <v>99.92499372602985</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.54159860440178</v>
+        <v>83.13483107810123</v>
       </c>
       <c r="C14" t="n">
-        <v>39.0876729755706</v>
+        <v>38.88319875206583</v>
       </c>
       <c r="D14" t="n">
-        <v>1.491542406123168</v>
+        <v>1.47459481068023</v>
       </c>
       <c r="E14" t="n">
-        <v>11.95116510811295</v>
+        <v>11.92102905866938</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554929224982727</v>
+        <v>0.7553619790776076</v>
       </c>
       <c r="G14" t="n">
-        <v>24.93699759855073</v>
+        <v>24.77498887567024</v>
       </c>
       <c r="H14" t="n">
-        <v>36.63732818479365</v>
+        <v>36.74410890906701</v>
       </c>
       <c r="I14" t="n">
-        <v>3.047241618708821</v>
+        <v>2.74373507570172</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721830765614206</v>
+        <v>4.721012369235046</v>
       </c>
       <c r="K14" t="n">
-        <v>16.45840139559818</v>
+        <v>16.86516892189877</v>
       </c>
       <c r="L14" t="n">
-        <v>44.35247425866716</v>
+        <v>44.16027499370767</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89854862983596</v>
+        <v>99.90864266767227</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.8173338705478</v>
+        <v>82.278982699447</v>
       </c>
       <c r="C15" t="n">
-        <v>38.83416130402956</v>
+        <v>38.45120066151294</v>
       </c>
       <c r="D15" t="n">
-        <v>1.464892689634758</v>
+        <v>1.442868478214851</v>
       </c>
       <c r="E15" t="n">
-        <v>12.16129202674695</v>
+        <v>12.04597231348755</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562658836270654</v>
+        <v>0.7560623181468114</v>
       </c>
       <c r="G15" t="n">
-        <v>24.49144277332729</v>
+        <v>24.24194784758402</v>
       </c>
       <c r="H15" t="n">
-        <v>36.67481262668097</v>
+        <v>36.77817646309391</v>
       </c>
       <c r="I15" t="n">
-        <v>2.541966097861608</v>
+        <v>2.288565790502308</v>
       </c>
       <c r="J15" t="n">
-        <v>4.72666177266916</v>
+        <v>4.725389488417569</v>
       </c>
       <c r="K15" t="n">
-        <v>17.18266612945218</v>
+        <v>17.72101730055297</v>
       </c>
       <c r="L15" t="n">
-        <v>43.89852696599854</v>
+        <v>43.75156717472016</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91535439948029</v>
+        <v>99.92378513678605</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.36856057184499</v>
+        <v>79.85416404472784</v>
       </c>
       <c r="C16" t="n">
-        <v>36.77817092155848</v>
+        <v>36.37988866250602</v>
       </c>
       <c r="D16" t="n">
-        <v>1.371989660950666</v>
+        <v>1.351216334350033</v>
       </c>
       <c r="E16" t="n">
-        <v>11.74338805543202</v>
+        <v>11.59891225466847</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569309076018418</v>
+        <v>0.7566646929578533</v>
       </c>
       <c r="G16" t="n">
-        <v>22.93820325852535</v>
+        <v>22.70208019835859</v>
       </c>
       <c r="H16" t="n">
-        <v>36.7070626993012</v>
+        <v>36.80747860732949</v>
       </c>
       <c r="I16" t="n">
-        <v>2.120167817522406</v>
+        <v>1.908657626076819</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730818172511513</v>
+        <v>4.729154330986582</v>
       </c>
       <c r="K16" t="n">
-        <v>19.63143942815501</v>
+        <v>20.14583595527216</v>
       </c>
       <c r="L16" t="n">
-        <v>43.51977948090147</v>
+        <v>43.41070411026341</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92938983061495</v>
+        <v>99.93642872804159</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.09089947426743</v>
+        <v>81.53621202136797</v>
       </c>
       <c r="C17" t="n">
-        <v>38.0147191448685</v>
+        <v>37.61346655428465</v>
       </c>
       <c r="D17" t="n">
-        <v>1.373184773062138</v>
+        <v>1.352254371880792</v>
       </c>
       <c r="E17" t="n">
-        <v>12.53501484742354</v>
+        <v>12.3671773545082</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575902546224275</v>
+        <v>0.7572459813344984</v>
       </c>
       <c r="G17" t="n">
-        <v>23.38204311351396</v>
+        <v>23.16568443415341</v>
       </c>
       <c r="H17" t="n">
-        <v>37.16289632592467</v>
+        <v>37.2819189561601</v>
       </c>
       <c r="I17" t="n">
-        <v>2.145231068330511</v>
+        <v>1.879143539990359</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734939091390173</v>
+        <v>4.732787383340613</v>
       </c>
       <c r="K17" t="n">
-        <v>17.90910052573257</v>
+        <v>18.46378797863202</v>
       </c>
       <c r="L17" t="n">
-        <v>44.0047348618057</v>
+        <v>43.8601554322836</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92855453240678</v>
+        <v>99.93740996520026</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.76803531863425</v>
+        <v>79.17303730499845</v>
       </c>
       <c r="C18" t="n">
-        <v>36.02291759247925</v>
+        <v>35.54017958383936</v>
       </c>
       <c r="D18" t="n">
-        <v>1.288609710975901</v>
+        <v>1.266452405208991</v>
       </c>
       <c r="E18" t="n">
-        <v>12.06114920209422</v>
+        <v>11.84363124546529</v>
       </c>
       <c r="F18" t="n">
-        <v>0.758156626416437</v>
+        <v>0.757745559614686</v>
       </c>
       <c r="G18" t="n">
-        <v>21.94193265873613</v>
+        <v>21.69579731448069</v>
       </c>
       <c r="H18" t="n">
-        <v>37.190679175736</v>
+        <v>37.30651497570106</v>
       </c>
       <c r="I18" t="n">
-        <v>1.789029029572826</v>
+        <v>1.566986056935939</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738478915102733</v>
+        <v>4.735909747591786</v>
       </c>
       <c r="K18" t="n">
-        <v>20.23196468136574</v>
+        <v>20.82696269500156</v>
       </c>
       <c r="L18" t="n">
-        <v>43.68552797425694</v>
+        <v>43.58065928949269</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94041024810193</v>
+        <v>99.9478015683336</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.80526479751055</v>
+        <v>78.24831932489133</v>
       </c>
       <c r="C19" t="n">
-        <v>35.33555393120631</v>
+        <v>34.84905530744675</v>
       </c>
       <c r="D19" t="n">
-        <v>1.254246895449403</v>
+        <v>1.233178761610724</v>
       </c>
       <c r="E19" t="n">
-        <v>11.9881526313747</v>
+        <v>11.75142974585278</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7586350279304962</v>
+        <v>0.7581696496766462</v>
       </c>
       <c r="G19" t="n">
-        <v>21.35681632923402</v>
+        <v>21.12578124087771</v>
       </c>
       <c r="H19" t="n">
-        <v>37.21414672400589</v>
+        <v>37.32739444117178</v>
       </c>
       <c r="I19" t="n">
-        <v>1.491798264950424</v>
+        <v>1.313805175222625</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741468924565603</v>
+        <v>4.738560310479038</v>
       </c>
       <c r="K19" t="n">
-        <v>21.19473520248946</v>
+        <v>21.75168067510867</v>
       </c>
       <c r="L19" t="n">
-        <v>43.42001561548275</v>
+        <v>43.35549500795582</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95030474917851</v>
+        <v>99.95623099051124</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.28737646042875</v>
+        <v>75.78292503755563</v>
       </c>
       <c r="C20" t="n">
-        <v>33.04715675037217</v>
+        <v>32.58563805168529</v>
       </c>
       <c r="D20" t="n">
-        <v>1.163603663029423</v>
+        <v>1.144599587184768</v>
       </c>
       <c r="E20" t="n">
-        <v>11.32908703287801</v>
+        <v>11.08988593741421</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7590473378455945</v>
+        <v>0.758534935393571</v>
       </c>
       <c r="G20" t="n">
-        <v>19.81337948812629</v>
+        <v>19.60831733404228</v>
       </c>
       <c r="H20" t="n">
-        <v>37.23437220939915</v>
+        <v>37.3453787591212</v>
       </c>
       <c r="I20" t="n">
-        <v>1.243840867615284</v>
+        <v>1.095365138189786</v>
       </c>
       <c r="J20" t="n">
-        <v>4.744045861534968</v>
+        <v>4.740843346209817</v>
       </c>
       <c r="K20" t="n">
-        <v>23.71262353957125</v>
+        <v>24.21707496244439</v>
       </c>
       <c r="L20" t="n">
-        <v>43.19878086936351</v>
+        <v>43.16079239766967</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95856115930694</v>
+        <v>99.96350541179935</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.17681221586606</v>
+        <v>81.73551662280713</v>
       </c>
       <c r="C21" t="n">
-        <v>36.64666676065318</v>
+        <v>36.37088542733577</v>
       </c>
       <c r="D21" t="n">
-        <v>1.16447922179491</v>
+        <v>1.14528477075995</v>
       </c>
       <c r="E21" t="n">
-        <v>13.28431952274972</v>
+        <v>13.1047485721734</v>
       </c>
       <c r="F21" t="n">
-        <v>0.759618486400026</v>
+        <v>0.7589890118101211</v>
       </c>
       <c r="G21" t="n">
-        <v>21.46582447754311</v>
+        <v>21.38363551912178</v>
       </c>
       <c r="H21" t="n">
-        <v>38.89992570248026</v>
+        <v>39.1313147561382</v>
       </c>
       <c r="I21" t="n">
-        <v>1.855029264897863</v>
+        <v>1.467862668990419</v>
       </c>
       <c r="J21" t="n">
-        <v>4.747615540000165</v>
+        <v>4.743681323813256</v>
       </c>
       <c r="K21" t="n">
-        <v>17.82318778413393</v>
+        <v>18.26448337719287</v>
       </c>
       <c r="L21" t="n">
-        <v>45.46835763890088</v>
+        <v>45.31573171219103</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93821218368799</v>
+        <v>99.95110051671968</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_1_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_1_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>44.78364146049694</v>
+        <v>45.68695438944611</v>
       </c>
       <c r="M2" t="n">
-        <v>100.7156374904775</v>
+        <v>99.34462423510709</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.9272438650878</v>
+        <v>88.04784175307746</v>
       </c>
       <c r="C3" t="n">
-        <v>45.81881193808258</v>
+        <v>45.92598919860135</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228557072459005</v>
+        <v>2.228785319187652</v>
       </c>
       <c r="E3" t="n">
-        <v>5.638374198469602</v>
+        <v>5.705975936159633</v>
       </c>
       <c r="F3" t="n">
-        <v>0.742852357486335</v>
+        <v>0.7429284397292175</v>
       </c>
       <c r="G3" t="n">
-        <v>33.93598195336965</v>
+        <v>33.97196467784574</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17120844437141</v>
+        <v>34.174708227544</v>
       </c>
       <c r="I3" t="n">
-        <v>6.567442604642203</v>
+        <v>6.580176404303619</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642827234289594</v>
+        <v>4.643302748307609</v>
       </c>
       <c r="K3" t="n">
-        <v>12.07275613491221</v>
+        <v>11.95215824692253</v>
       </c>
       <c r="L3" t="n">
-        <v>48.87267605839214</v>
+        <v>48.88566376239623</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7642441313869</v>
+        <v>106.7638112079201</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.9401045826849</v>
+        <v>87.23328018627075</v>
       </c>
       <c r="C4" t="n">
-        <v>42.470771105582</v>
+        <v>42.74900619560216</v>
       </c>
       <c r="D4" t="n">
-        <v>2.180507065434758</v>
+        <v>2.190052213149424</v>
       </c>
       <c r="E4" t="n">
-        <v>6.430867800668595</v>
+        <v>6.52264658507236</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444143839348336</v>
+        <v>0.7444883900291764</v>
       </c>
       <c r="G4" t="n">
-        <v>33.20428690665725</v>
+        <v>33.38158044529276</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24306166100234</v>
+        <v>34.24646594134212</v>
       </c>
       <c r="I4" t="n">
-        <v>5.48437686539441</v>
+        <v>5.494994173702556</v>
       </c>
       <c r="J4" t="n">
-        <v>4.65258989959271</v>
+        <v>4.653052437682352</v>
       </c>
       <c r="K4" t="n">
-        <v>13.0598954173151</v>
+        <v>12.76671981372923</v>
       </c>
       <c r="L4" t="n">
-        <v>44.28690451586284</v>
+        <v>44.3014913127713</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81757103875994</v>
+        <v>99.81721732210271</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.75215120938769</v>
+        <v>86.21421178727964</v>
       </c>
       <c r="C5" t="n">
-        <v>42.13384179248078</v>
+        <v>42.58289286978905</v>
       </c>
       <c r="D5" t="n">
-        <v>2.122330849158962</v>
+        <v>2.140823062733537</v>
       </c>
       <c r="E5" t="n">
-        <v>7.022366055679306</v>
+        <v>7.140574324689357</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457392340812312</v>
+        <v>0.7458088139549166</v>
       </c>
       <c r="G5" t="n">
-        <v>32.31839214988877</v>
+        <v>32.63121164814974</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30400476773663</v>
+        <v>34.30720544192616</v>
       </c>
       <c r="I5" t="n">
-        <v>4.578447939835085</v>
+        <v>4.587283408607701</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660870213007694</v>
+        <v>4.661305087218228</v>
       </c>
       <c r="K5" t="n">
-        <v>14.24784879061232</v>
+        <v>13.78578821272037</v>
       </c>
       <c r="L5" t="n">
-        <v>43.4659656150904</v>
+        <v>43.47868019044326</v>
       </c>
       <c r="M5" t="n">
-        <v>99.8476561981835</v>
+        <v>99.84736127295268</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.39341054064634</v>
+        <v>85.0612273152469</v>
       </c>
       <c r="C6" t="n">
-        <v>41.48598316726624</v>
+        <v>42.14255607313472</v>
       </c>
       <c r="D6" t="n">
-        <v>2.055880479858517</v>
+        <v>2.085054104452929</v>
       </c>
       <c r="E6" t="n">
-        <v>7.43935041925192</v>
+        <v>7.592639195935134</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468647436721313</v>
+        <v>0.7469277364720953</v>
       </c>
       <c r="G6" t="n">
-        <v>31.30650039210381</v>
+        <v>31.78116069684519</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35577820891803</v>
+        <v>34.35867587771639</v>
       </c>
       <c r="I6" t="n">
-        <v>3.821131648891108</v>
+        <v>3.828471350874547</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667904647950819</v>
+        <v>4.668298352950594</v>
       </c>
       <c r="K6" t="n">
-        <v>15.60658945935367</v>
+        <v>14.93877268475315</v>
       </c>
       <c r="L6" t="n">
-        <v>42.78024826394022</v>
+        <v>42.79124670298414</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87282089056013</v>
+        <v>99.872575460872</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.8748128234304</v>
+        <v>83.67449965963812</v>
       </c>
       <c r="C7" t="n">
-        <v>40.56071104668311</v>
+        <v>41.35078621016254</v>
       </c>
       <c r="D7" t="n">
-        <v>1.981901095884731</v>
+        <v>2.017877244760397</v>
       </c>
       <c r="E7" t="n">
-        <v>7.703044047183726</v>
+        <v>7.880426209475508</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478225230468343</v>
+        <v>0.7478782552102681</v>
       </c>
       <c r="G7" t="n">
-        <v>30.1799584379031</v>
+        <v>30.75722632102334</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39983606015437</v>
+        <v>34.40239973967233</v>
       </c>
       <c r="I7" t="n">
-        <v>3.188359890214935</v>
+        <v>3.1944527944321</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673890769042713</v>
+        <v>4.674239095064173</v>
       </c>
       <c r="K7" t="n">
-        <v>17.1251871765696</v>
+        <v>16.32550034036187</v>
       </c>
       <c r="L7" t="n">
-        <v>42.20795923094477</v>
+        <v>42.21736702306244</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89385745419747</v>
+        <v>99.89365357358685</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.65354761351871</v>
+        <v>88.60685626436666</v>
       </c>
       <c r="C8" t="n">
-        <v>42.83978446739091</v>
+        <v>43.66042189316843</v>
       </c>
       <c r="D8" t="n">
-        <v>1.986096596755063</v>
+        <v>2.022198577940456</v>
       </c>
       <c r="E8" t="n">
-        <v>9.516456626220377</v>
+        <v>9.72145677060236</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494055939946287</v>
+        <v>0.7494798546768741</v>
       </c>
       <c r="G8" t="n">
-        <v>30.67851350229749</v>
+        <v>31.2607865449435</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47265732375291</v>
+        <v>34.47607331513621</v>
       </c>
       <c r="I8" t="n">
-        <v>5.566633008031797</v>
+        <v>5.692612109336781</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683784962466428</v>
+        <v>4.684249091730461</v>
       </c>
       <c r="K8" t="n">
-        <v>12.3464523864813</v>
+        <v>11.39314373563334</v>
       </c>
       <c r="L8" t="n">
-        <v>44.62860068429132</v>
+        <v>44.75708612808656</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81483753816353</v>
+        <v>99.81065175688833</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.64733739462436</v>
+        <v>86.84051572675676</v>
       </c>
       <c r="C9" t="n">
-        <v>41.69740557371095</v>
+        <v>42.77822178129452</v>
       </c>
       <c r="D9" t="n">
-        <v>1.895055492837601</v>
+        <v>1.942677343886437</v>
       </c>
       <c r="E9" t="n">
-        <v>9.85477158895665</v>
+        <v>10.13125165237362</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7507610266454134</v>
+        <v>0.7508470740080005</v>
       </c>
       <c r="G9" t="n">
-        <v>29.27223460309429</v>
+        <v>30.03148278087648</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53500722568901</v>
+        <v>34.53896540436803</v>
       </c>
       <c r="I9" t="n">
-        <v>4.647251040867544</v>
+        <v>4.752497258694187</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692256416533833</v>
+        <v>4.692794212550002</v>
       </c>
       <c r="K9" t="n">
-        <v>14.35266260537566</v>
+        <v>13.15948427324323</v>
       </c>
       <c r="L9" t="n">
-        <v>43.79530312624583</v>
+        <v>43.90416583131399</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84537130533245</v>
+        <v>99.84187188585175</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.45361185039474</v>
+        <v>84.82917812003356</v>
       </c>
       <c r="C10" t="n">
-        <v>40.22454870075819</v>
+        <v>41.5049903081289</v>
       </c>
       <c r="D10" t="n">
-        <v>1.796493037014052</v>
+        <v>1.852760720474483</v>
       </c>
       <c r="E10" t="n">
-        <v>9.988673193951941</v>
+        <v>10.32342558421864</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519241412890455</v>
+        <v>0.7520173869203192</v>
       </c>
       <c r="G10" t="n">
-        <v>27.74977611001665</v>
+        <v>28.6414786527033</v>
       </c>
       <c r="H10" t="n">
-        <v>34.58851049929609</v>
+        <v>34.59279979833468</v>
       </c>
       <c r="I10" t="n">
-        <v>3.878708985770422</v>
+        <v>3.966587309130164</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699525883056533</v>
+        <v>4.700108668251993</v>
       </c>
       <c r="K10" t="n">
-        <v>16.54638814960526</v>
+        <v>15.17082187996641</v>
       </c>
       <c r="L10" t="n">
-        <v>43.0999728429458</v>
+        <v>43.19217399916319</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87090969330924</v>
+        <v>99.8679861872585</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.99213201522286</v>
+        <v>82.67526791906904</v>
       </c>
       <c r="C11" t="n">
-        <v>38.3640962284568</v>
+        <v>39.96668704739805</v>
       </c>
       <c r="D11" t="n">
-        <v>1.686885845092572</v>
+        <v>1.757334295672777</v>
       </c>
       <c r="E11" t="n">
-        <v>9.918673887002441</v>
+        <v>10.34336773839754</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529257405812464</v>
+        <v>0.7530209529842695</v>
       </c>
       <c r="G11" t="n">
-        <v>26.05671358586455</v>
+        <v>27.16629954368056</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63458406673733</v>
+        <v>34.6389638372764</v>
       </c>
       <c r="I11" t="n">
-        <v>3.236563011311928</v>
+        <v>3.309900594905824</v>
       </c>
       <c r="J11" t="n">
-        <v>4.705785878632789</v>
+        <v>4.706380956151683</v>
       </c>
       <c r="K11" t="n">
-        <v>19.00786798477715</v>
+        <v>17.32473208093094</v>
       </c>
       <c r="L11" t="n">
-        <v>42.52029387049464</v>
+        <v>42.59839789086181</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89225808372859</v>
+        <v>99.88981701919082</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.56341349043589</v>
+        <v>80.4615547841469</v>
       </c>
       <c r="C12" t="n">
-        <v>36.43600317421384</v>
+        <v>38.26601781177214</v>
       </c>
       <c r="D12" t="n">
-        <v>1.57991200014272</v>
+        <v>1.660159996186106</v>
       </c>
       <c r="E12" t="n">
-        <v>9.739718949266566</v>
+        <v>10.23165082282797</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7537883429331784</v>
+        <v>0.7538823981402779</v>
       </c>
       <c r="G12" t="n">
-        <v>24.40432741690952</v>
+        <v>25.66410036945254</v>
       </c>
       <c r="H12" t="n">
-        <v>34.6742637749262</v>
+        <v>34.67859031445279</v>
       </c>
       <c r="I12" t="n">
-        <v>2.700225862925341</v>
+        <v>2.761405894710499</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711177143332364</v>
+        <v>4.711764988376736</v>
       </c>
       <c r="K12" t="n">
-        <v>21.43658650956411</v>
+        <v>19.53844521585308</v>
       </c>
       <c r="L12" t="n">
-        <v>42.03750578813006</v>
+        <v>42.10359528918293</v>
       </c>
       <c r="M12" t="n">
-        <v>99.91009547190801</v>
+        <v>99.90805831680817</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.11258644056767</v>
+        <v>78.13640610012207</v>
       </c>
       <c r="C13" t="n">
-        <v>34.4019510292345</v>
+        <v>36.36817349906961</v>
       </c>
       <c r="D13" t="n">
-        <v>1.472974370169063</v>
+        <v>1.558907103612677</v>
       </c>
       <c r="E13" t="n">
-        <v>9.455879457476449</v>
+        <v>9.991529548618574</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545319075605861</v>
+        <v>0.7546232041045972</v>
       </c>
       <c r="G13" t="n">
-        <v>22.75250064755166</v>
+        <v>24.09885099368661</v>
       </c>
       <c r="H13" t="n">
-        <v>34.70846774778695</v>
+        <v>34.71266738881148</v>
       </c>
       <c r="I13" t="n">
-        <v>2.252407887769297</v>
+        <v>2.303432835634414</v>
       </c>
       <c r="J13" t="n">
-        <v>4.715824422253662</v>
+        <v>4.716395025653731</v>
       </c>
       <c r="K13" t="n">
-        <v>23.88741355943234</v>
+        <v>21.86359389987793</v>
       </c>
       <c r="L13" t="n">
-        <v>41.63562913736302</v>
+        <v>41.69152688175495</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92499372602985</v>
+        <v>99.92329428070248</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.13483107810123</v>
+        <v>84.42932433101289</v>
       </c>
       <c r="C14" t="n">
-        <v>38.88319875206583</v>
+        <v>40.32601951815648</v>
       </c>
       <c r="D14" t="n">
-        <v>1.47459481068023</v>
+        <v>1.560666857494521</v>
       </c>
       <c r="E14" t="n">
-        <v>11.92102905866938</v>
+        <v>12.20434403122721</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7553619790776076</v>
+        <v>0.7554750516006252</v>
       </c>
       <c r="G14" t="n">
-        <v>24.77498887567024</v>
+        <v>25.85105512893999</v>
       </c>
       <c r="H14" t="n">
-        <v>36.74410890906701</v>
+        <v>36.47685280541204</v>
       </c>
       <c r="I14" t="n">
-        <v>2.74373507570172</v>
+        <v>2.859211383834618</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721012369235046</v>
+        <v>4.721719072503906</v>
       </c>
       <c r="K14" t="n">
-        <v>16.86516892189877</v>
+        <v>15.57067566898709</v>
       </c>
       <c r="L14" t="n">
-        <v>44.16027499370767</v>
+        <v>44.00810523165207</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90864266767227</v>
+        <v>99.90480041879565</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.278982699447</v>
+        <v>83.74074612620826</v>
       </c>
       <c r="C15" t="n">
-        <v>38.45120066151294</v>
+        <v>40.08007555665697</v>
       </c>
       <c r="D15" t="n">
-        <v>1.442868478214851</v>
+        <v>1.53499630135497</v>
       </c>
       <c r="E15" t="n">
-        <v>12.04597231348755</v>
+        <v>12.40109113145127</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7560623181468114</v>
+        <v>0.7561922497485024</v>
       </c>
       <c r="G15" t="n">
-        <v>24.24194784758402</v>
+        <v>25.42584525229825</v>
       </c>
       <c r="H15" t="n">
-        <v>36.77817646309391</v>
+        <v>36.51148152176343</v>
       </c>
       <c r="I15" t="n">
-        <v>2.288565790502308</v>
+        <v>2.384938108663723</v>
       </c>
       <c r="J15" t="n">
-        <v>4.725389488417569</v>
+        <v>4.726201560928138</v>
       </c>
       <c r="K15" t="n">
-        <v>17.72101730055297</v>
+        <v>16.25925387379172</v>
       </c>
       <c r="L15" t="n">
-        <v>43.75156717472016</v>
+        <v>43.58124803111146</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92378513678605</v>
+        <v>99.92057746156016</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.85416404472784</v>
+        <v>81.44249438552056</v>
       </c>
       <c r="C16" t="n">
-        <v>36.37988866250602</v>
+        <v>38.15111459814636</v>
       </c>
       <c r="D16" t="n">
-        <v>1.351216334350033</v>
+        <v>1.446548110619059</v>
       </c>
       <c r="E16" t="n">
-        <v>11.59891225466847</v>
+        <v>12.01803756231276</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7566646929578533</v>
+        <v>0.75680786473316</v>
       </c>
       <c r="G16" t="n">
-        <v>22.70208019835859</v>
+        <v>23.96077982607415</v>
       </c>
       <c r="H16" t="n">
-        <v>36.80747860732949</v>
+        <v>36.54120546450989</v>
       </c>
       <c r="I16" t="n">
-        <v>1.908657626076819</v>
+        <v>1.989066402689294</v>
       </c>
       <c r="J16" t="n">
-        <v>4.729154330986582</v>
+        <v>4.730049154582248</v>
       </c>
       <c r="K16" t="n">
-        <v>20.14583595527216</v>
+        <v>18.55750561447942</v>
       </c>
       <c r="L16" t="n">
-        <v>43.41070411026341</v>
+        <v>43.225131506578</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93642872804159</v>
+        <v>99.9337517192038</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.53621202136797</v>
+        <v>83.02201844940622</v>
       </c>
       <c r="C17" t="n">
-        <v>37.61346655428465</v>
+        <v>39.31214430019385</v>
       </c>
       <c r="D17" t="n">
-        <v>1.352254371880792</v>
+        <v>1.447694477268464</v>
       </c>
       <c r="E17" t="n">
-        <v>12.3671773545082</v>
+        <v>12.75747899152058</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7572459813344984</v>
+        <v>0.7574076230749451</v>
       </c>
       <c r="G17" t="n">
-        <v>23.16568443415341</v>
+        <v>24.38071746501272</v>
       </c>
       <c r="H17" t="n">
-        <v>37.2819189561601</v>
+        <v>36.97111289310243</v>
       </c>
       <c r="I17" t="n">
-        <v>1.879143539990359</v>
+        <v>1.973809355208685</v>
       </c>
       <c r="J17" t="n">
-        <v>4.732787383340613</v>
+        <v>4.733797644218405</v>
       </c>
       <c r="K17" t="n">
-        <v>18.46378797863202</v>
+        <v>16.97798155059377</v>
       </c>
       <c r="L17" t="n">
-        <v>43.8601554322836</v>
+        <v>43.64413260318103</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93740996520026</v>
+        <v>99.93425845396865</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.17303730499845</v>
+        <v>80.80144258707855</v>
       </c>
       <c r="C18" t="n">
-        <v>35.54017958383936</v>
+        <v>37.39686288277245</v>
       </c>
       <c r="D18" t="n">
-        <v>1.266452405208991</v>
+        <v>1.365307675146158</v>
       </c>
       <c r="E18" t="n">
-        <v>11.84363124546529</v>
+        <v>12.30579033060215</v>
       </c>
       <c r="F18" t="n">
-        <v>0.757745559614686</v>
+        <v>0.7579219130411816</v>
       </c>
       <c r="G18" t="n">
-        <v>21.69579731448069</v>
+        <v>22.99323593701807</v>
       </c>
       <c r="H18" t="n">
-        <v>37.30651497570106</v>
+        <v>36.99621677616651</v>
       </c>
       <c r="I18" t="n">
-        <v>1.566986056935939</v>
+        <v>1.6459579985971</v>
       </c>
       <c r="J18" t="n">
-        <v>4.735909747591786</v>
+        <v>4.737011956507382</v>
       </c>
       <c r="K18" t="n">
-        <v>20.82696269500156</v>
+        <v>19.19855741292146</v>
       </c>
       <c r="L18" t="n">
-        <v>43.58065928949269</v>
+        <v>43.3497516666614</v>
       </c>
       <c r="M18" t="n">
-        <v>99.9478015683336</v>
+        <v>99.9451719623553</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.24831932489133</v>
+        <v>79.88010181907404</v>
       </c>
       <c r="C19" t="n">
-        <v>34.84905530744675</v>
+        <v>36.72952036538598</v>
       </c>
       <c r="D19" t="n">
-        <v>1.233178761610724</v>
+        <v>1.331761018692021</v>
       </c>
       <c r="E19" t="n">
-        <v>11.75142974585278</v>
+        <v>12.23216382603419</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7581696496766462</v>
+        <v>0.7583559740250831</v>
       </c>
       <c r="G19" t="n">
-        <v>21.12578124087771</v>
+        <v>22.42827449954172</v>
       </c>
       <c r="H19" t="n">
-        <v>37.32739444117178</v>
+        <v>37.01740446579282</v>
       </c>
       <c r="I19" t="n">
-        <v>1.313805175222625</v>
+        <v>1.372417197331446</v>
       </c>
       <c r="J19" t="n">
-        <v>4.738560310479038</v>
+        <v>4.739724837656767</v>
       </c>
       <c r="K19" t="n">
-        <v>21.75168067510867</v>
+        <v>20.11989818092596</v>
       </c>
       <c r="L19" t="n">
-        <v>43.35549500795582</v>
+        <v>43.10486039817147</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95623099051124</v>
+        <v>99.95427894448341</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.78292503755563</v>
+        <v>77.40366287006556</v>
       </c>
       <c r="C20" t="n">
-        <v>32.58563805168529</v>
+        <v>34.46472986891389</v>
       </c>
       <c r="D20" t="n">
-        <v>1.144599587184768</v>
+        <v>1.240740448948875</v>
       </c>
       <c r="E20" t="n">
-        <v>11.08988593741421</v>
+        <v>11.58685149745665</v>
       </c>
       <c r="F20" t="n">
-        <v>0.758534935393571</v>
+        <v>0.7587296620672163</v>
       </c>
       <c r="G20" t="n">
-        <v>19.60831733404228</v>
+        <v>20.89539112583482</v>
       </c>
       <c r="H20" t="n">
-        <v>37.3453787591212</v>
+        <v>37.03564518898018</v>
       </c>
       <c r="I20" t="n">
-        <v>1.095365138189786</v>
+        <v>1.144244558857705</v>
       </c>
       <c r="J20" t="n">
-        <v>4.740843346209817</v>
+        <v>4.742060387920099</v>
       </c>
       <c r="K20" t="n">
-        <v>24.21707496244439</v>
+        <v>22.59633712993446</v>
       </c>
       <c r="L20" t="n">
-        <v>43.16079239766967</v>
+        <v>42.9008103012258</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96350541179935</v>
+        <v>99.96187730007414</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.73551662280713</v>
+        <v>82.910540997589</v>
       </c>
       <c r="C21" t="n">
-        <v>36.37088542733577</v>
+        <v>37.90569856144194</v>
       </c>
       <c r="D21" t="n">
-        <v>1.14528477075995</v>
+        <v>1.241536532754218</v>
       </c>
       <c r="E21" t="n">
-        <v>13.1047485721734</v>
+        <v>13.44036985437121</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7589890118101211</v>
+        <v>0.7592164781431465</v>
       </c>
       <c r="G21" t="n">
-        <v>21.38363551912178</v>
+        <v>22.48889674799412</v>
       </c>
       <c r="H21" t="n">
-        <v>39.1313147561382</v>
+        <v>38.63950671989114</v>
       </c>
       <c r="I21" t="n">
-        <v>1.467862668990419</v>
+        <v>1.595911676040507</v>
       </c>
       <c r="J21" t="n">
-        <v>4.743681323813256</v>
+        <v>4.745102988394663</v>
       </c>
       <c r="K21" t="n">
-        <v>18.26448337719287</v>
+        <v>17.08945900241099</v>
       </c>
       <c r="L21" t="n">
-        <v>45.31573171219103</v>
+        <v>44.95167949068463</v>
       </c>
       <c r="M21" t="n">
-        <v>99.95110051671968</v>
+        <v>99.94683705453757</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_1_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_1_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.68695438944611</v>
+        <v>44.17723862001359</v>
       </c>
       <c r="M2" t="n">
-        <v>99.34462423510709</v>
+        <v>94.02424801355167</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.04784175307746</v>
+        <v>81.46104510335634</v>
       </c>
       <c r="C3" t="n">
-        <v>45.92598919860135</v>
+        <v>43.2166006589119</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228785319187652</v>
+        <v>2.1795966241908</v>
       </c>
       <c r="E3" t="n">
-        <v>5.705975936159633</v>
+        <v>4.14489839153666</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429284397292175</v>
+        <v>0.737621785754873</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97196467784574</v>
+        <v>32.78476588886993</v>
       </c>
       <c r="H3" t="n">
-        <v>34.174708227544</v>
+        <v>33.93060214472415</v>
       </c>
       <c r="I3" t="n">
-        <v>6.580176404303619</v>
+        <v>3.073424107311971</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643302748307609</v>
+        <v>4.610136160967956</v>
       </c>
       <c r="K3" t="n">
-        <v>11.95215824692253</v>
+        <v>18.53895489664365</v>
       </c>
       <c r="L3" t="n">
-        <v>48.88566376239623</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7638112079201</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.23328018627075</v>
+        <v>88.57603757580989</v>
       </c>
       <c r="C4" t="n">
-        <v>42.74900619560216</v>
+        <v>42.8330784384442</v>
       </c>
       <c r="D4" t="n">
-        <v>2.190052213149424</v>
+        <v>2.185328611802338</v>
       </c>
       <c r="E4" t="n">
-        <v>6.52264658507236</v>
+        <v>6.540065936559322</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444883900291764</v>
+        <v>0.7395616120929311</v>
       </c>
       <c r="G4" t="n">
-        <v>33.38158044529276</v>
+        <v>33.48076636646372</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24646594134212</v>
+        <v>34.01983415627483</v>
       </c>
       <c r="I4" t="n">
-        <v>5.494994173702556</v>
+        <v>6.988220817035936</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653052437682352</v>
+        <v>4.622260075580819</v>
       </c>
       <c r="K4" t="n">
-        <v>12.76671981372923</v>
+        <v>11.4239624241901</v>
       </c>
       <c r="L4" t="n">
-        <v>44.3014913127713</v>
+        <v>45.51062943311815</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81721732210271</v>
+        <v>99.76767029575247</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.21421178727964</v>
+        <v>87.45084440936307</v>
       </c>
       <c r="C5" t="n">
-        <v>42.58289286978905</v>
+        <v>42.79111558505982</v>
       </c>
       <c r="D5" t="n">
-        <v>2.140823062733537</v>
+        <v>2.131800968345385</v>
       </c>
       <c r="E5" t="n">
-        <v>7.140574324689357</v>
+        <v>7.35261840634141</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458088139549166</v>
+        <v>0.7412068911132614</v>
       </c>
       <c r="G5" t="n">
-        <v>32.63121164814974</v>
+        <v>32.66068534292761</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30720544192616</v>
+        <v>34.09551699121002</v>
       </c>
       <c r="I5" t="n">
-        <v>4.587283408607701</v>
+        <v>5.83647273996751</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661305087218228</v>
+        <v>4.632543069457883</v>
       </c>
       <c r="K5" t="n">
-        <v>13.78578821272037</v>
+        <v>12.54915559063692</v>
       </c>
       <c r="L5" t="n">
-        <v>43.47868019044326</v>
+        <v>44.46561157938559</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84736127295268</v>
+        <v>99.80588275508234</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>85.0612273152469</v>
+        <v>86.10967399709858</v>
       </c>
       <c r="C6" t="n">
-        <v>42.14255607313472</v>
+        <v>42.35576241034755</v>
       </c>
       <c r="D6" t="n">
-        <v>2.085054104452929</v>
+        <v>2.067854620008915</v>
       </c>
       <c r="E6" t="n">
-        <v>7.592639195935134</v>
+        <v>7.944216646758853</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469277364720953</v>
+        <v>0.7426050415702115</v>
       </c>
       <c r="G6" t="n">
-        <v>31.78116069684519</v>
+        <v>31.68098245656119</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35867587771639</v>
+        <v>34.15983191222972</v>
       </c>
       <c r="I6" t="n">
-        <v>3.828471350874547</v>
+        <v>4.872901810155868</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668298352950594</v>
+        <v>4.641281509813821</v>
       </c>
       <c r="K6" t="n">
-        <v>14.93877268475315</v>
+        <v>13.89032600290141</v>
       </c>
       <c r="L6" t="n">
-        <v>42.79124670298414</v>
+        <v>43.59178734397416</v>
       </c>
       <c r="M6" t="n">
-        <v>99.872575460872</v>
+        <v>99.83787575722313</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.67449965963812</v>
+        <v>84.60007767543301</v>
       </c>
       <c r="C7" t="n">
-        <v>41.35078621016254</v>
+        <v>41.6028543613108</v>
       </c>
       <c r="D7" t="n">
-        <v>2.017877244760397</v>
+        <v>1.996176859827308</v>
       </c>
       <c r="E7" t="n">
-        <v>7.880426209475508</v>
+        <v>8.346723864700495</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478782552102681</v>
+        <v>0.7437950984239415</v>
       </c>
       <c r="G7" t="n">
-        <v>30.75722632102334</v>
+        <v>30.58282892058906</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40239973967233</v>
+        <v>34.21457452750131</v>
       </c>
       <c r="I7" t="n">
-        <v>3.1944527944321</v>
+        <v>4.067259039241257</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674239095064173</v>
+        <v>4.648719365149634</v>
       </c>
       <c r="K7" t="n">
-        <v>16.32550034036187</v>
+        <v>15.39992232456699</v>
       </c>
       <c r="L7" t="n">
-        <v>42.21736702306244</v>
+        <v>42.86186493050677</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89365357358685</v>
+        <v>99.86464161638456</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.60685626436666</v>
+        <v>82.93788684551161</v>
       </c>
       <c r="C8" t="n">
-        <v>43.66042189316843</v>
+        <v>40.57223100240289</v>
       </c>
       <c r="D8" t="n">
-        <v>2.022198577940456</v>
+        <v>1.917714855444795</v>
       </c>
       <c r="E8" t="n">
-        <v>9.72145677060236</v>
+        <v>8.584314030366865</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494798546768741</v>
+        <v>0.7448096910116065</v>
       </c>
       <c r="G8" t="n">
-        <v>31.2607865449435</v>
+        <v>29.38073600733662</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47607331513621</v>
+        <v>34.2612457865339</v>
       </c>
       <c r="I8" t="n">
-        <v>5.692612109336781</v>
+        <v>3.394005905995288</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684249091730461</v>
+        <v>4.655060568822541</v>
       </c>
       <c r="K8" t="n">
-        <v>11.39314373563334</v>
+        <v>17.0621131544884</v>
       </c>
       <c r="L8" t="n">
-        <v>44.75708612808656</v>
+        <v>42.25267642535199</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81065175688833</v>
+        <v>99.88702058224328</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.84051572675676</v>
+        <v>81.07443184562696</v>
       </c>
       <c r="C9" t="n">
-        <v>42.77822178129452</v>
+        <v>39.23550929344127</v>
       </c>
       <c r="D9" t="n">
-        <v>1.942677343886437</v>
+        <v>1.830241167666737</v>
       </c>
       <c r="E9" t="n">
-        <v>10.13125165237362</v>
+        <v>8.664691922878939</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508470740080005</v>
+        <v>0.7456768062409677</v>
       </c>
       <c r="G9" t="n">
-        <v>30.03148278087648</v>
+        <v>28.04057778678657</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53896540436803</v>
+        <v>34.30113308708451</v>
       </c>
       <c r="I9" t="n">
-        <v>4.752497258694187</v>
+        <v>2.831631035963196</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692794212550002</v>
+        <v>4.660480039006048</v>
       </c>
       <c r="K9" t="n">
-        <v>13.15948427324323</v>
+        <v>18.92556815437303</v>
       </c>
       <c r="L9" t="n">
-        <v>43.90416583131399</v>
+        <v>41.74464461035252</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84187188585175</v>
+        <v>99.90572205816682</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.82917812003356</v>
+        <v>85.95658996460149</v>
       </c>
       <c r="C10" t="n">
-        <v>41.5049903081289</v>
+        <v>42.56427976252331</v>
       </c>
       <c r="D10" t="n">
-        <v>1.852760720474483</v>
+        <v>1.832327344206824</v>
       </c>
       <c r="E10" t="n">
-        <v>10.32342558421864</v>
+        <v>10.56292664020594</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520173869203192</v>
+        <v>0.7465267562296076</v>
       </c>
       <c r="G10" t="n">
-        <v>28.6414786527033</v>
+        <v>29.47101536139671</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59279979833468</v>
+        <v>35.73870667405527</v>
       </c>
       <c r="I10" t="n">
-        <v>3.966587309130164</v>
+        <v>2.939294962072099</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700108668251993</v>
+        <v>4.665792226435048</v>
       </c>
       <c r="K10" t="n">
-        <v>15.17082187996641</v>
+        <v>14.0434100353985</v>
       </c>
       <c r="L10" t="n">
-        <v>43.19217399916319</v>
+        <v>43.29444525342862</v>
       </c>
       <c r="M10" t="n">
-        <v>99.8679861872585</v>
+        <v>99.90213505135043</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.67526791906904</v>
+        <v>85.7066468165773</v>
       </c>
       <c r="C11" t="n">
-        <v>39.96668704739805</v>
+        <v>42.66834110505658</v>
       </c>
       <c r="D11" t="n">
-        <v>1.757334295672777</v>
+        <v>1.813822422357294</v>
       </c>
       <c r="E11" t="n">
-        <v>10.34336773839754</v>
+        <v>10.92431591442852</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530209529842695</v>
+        <v>0.7472531593158918</v>
       </c>
       <c r="G11" t="n">
-        <v>27.16629954368056</v>
+        <v>29.22446776541303</v>
       </c>
       <c r="H11" t="n">
-        <v>34.6389638372764</v>
+        <v>35.82456617101438</v>
       </c>
       <c r="I11" t="n">
-        <v>3.309900594905824</v>
+        <v>2.501889138323865</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706380956151683</v>
+        <v>4.670332245724324</v>
       </c>
       <c r="K11" t="n">
-        <v>17.32473208093094</v>
+        <v>14.29335318342269</v>
       </c>
       <c r="L11" t="n">
-        <v>42.59839789086181</v>
+        <v>42.95499047626681</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88981701919082</v>
+        <v>99.91668476474609</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>80.4615547841469</v>
+        <v>83.86335659699166</v>
       </c>
       <c r="C12" t="n">
-        <v>38.26601781177214</v>
+        <v>41.21405364447408</v>
       </c>
       <c r="D12" t="n">
-        <v>1.660159996186106</v>
+        <v>1.735584961706412</v>
       </c>
       <c r="E12" t="n">
-        <v>10.23165082282797</v>
+        <v>10.80087900425248</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538823981402779</v>
+        <v>0.7478729158662354</v>
       </c>
       <c r="G12" t="n">
-        <v>25.66410036945254</v>
+        <v>27.96389885929711</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67859031445279</v>
+        <v>35.85427833652471</v>
       </c>
       <c r="I12" t="n">
-        <v>2.761405894710499</v>
+        <v>2.08663679518076</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711764988376736</v>
+        <v>4.674205724163972</v>
       </c>
       <c r="K12" t="n">
-        <v>19.53844521585308</v>
+        <v>16.13664340300834</v>
       </c>
       <c r="L12" t="n">
-        <v>42.10359528918293</v>
+        <v>42.57980603200859</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90805831680817</v>
+        <v>99.930503079491</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>78.13640610012207</v>
+        <v>85.06392604703805</v>
       </c>
       <c r="C13" t="n">
-        <v>36.36817349906961</v>
+        <v>42.21021115384766</v>
       </c>
       <c r="D13" t="n">
-        <v>1.558907103612677</v>
+        <v>1.736906270341187</v>
       </c>
       <c r="E13" t="n">
-        <v>9.991529548618574</v>
+        <v>11.45235451986355</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546232041045972</v>
+        <v>0.7484422748796238</v>
       </c>
       <c r="G13" t="n">
-        <v>24.09885099368661</v>
+        <v>28.30464291229763</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71266738881148</v>
+        <v>36.20102937089747</v>
       </c>
       <c r="I13" t="n">
-        <v>2.303432835634414</v>
+        <v>1.942786480760949</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716395025653731</v>
+        <v>4.677764217997649</v>
       </c>
       <c r="K13" t="n">
-        <v>21.86359389987793</v>
+        <v>14.93607395296196</v>
       </c>
       <c r="L13" t="n">
-        <v>41.69152688175495</v>
+        <v>42.7890046080627</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92329428070248</v>
+        <v>99.93528971487231</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>84.42932433101289</v>
+        <v>83.19006420394216</v>
       </c>
       <c r="C14" t="n">
-        <v>40.32601951815648</v>
+        <v>40.63831558994735</v>
       </c>
       <c r="D14" t="n">
-        <v>1.560666857494521</v>
+        <v>1.659544266642027</v>
       </c>
       <c r="E14" t="n">
-        <v>12.20434403122721</v>
+        <v>11.2122719531315</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554750516006252</v>
+        <v>0.7489281126169708</v>
       </c>
       <c r="G14" t="n">
-        <v>25.85105512893999</v>
+        <v>27.04395088355939</v>
       </c>
       <c r="H14" t="n">
-        <v>36.47685280541204</v>
+        <v>36.22452861297598</v>
       </c>
       <c r="I14" t="n">
-        <v>2.859211383834618</v>
+        <v>1.620039671160212</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721719072503906</v>
+        <v>4.680800703856067</v>
       </c>
       <c r="K14" t="n">
-        <v>15.57067566898709</v>
+        <v>16.80993579605784</v>
       </c>
       <c r="L14" t="n">
-        <v>44.00810523165207</v>
+        <v>42.49778232286258</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90480041879565</v>
+        <v>99.94603370886777</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.74074612620826</v>
+        <v>82.37614626973635</v>
       </c>
       <c r="C15" t="n">
-        <v>40.08007555665697</v>
+        <v>40.05370110409736</v>
       </c>
       <c r="D15" t="n">
-        <v>1.53499630135497</v>
+        <v>1.625540607160072</v>
       </c>
       <c r="E15" t="n">
-        <v>12.40109113145127</v>
+        <v>11.21122920318231</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7561922497485024</v>
+        <v>0.7493439498722688</v>
       </c>
       <c r="G15" t="n">
-        <v>25.42584525229825</v>
+        <v>26.48982688977645</v>
       </c>
       <c r="H15" t="n">
-        <v>36.51148152176343</v>
+        <v>36.24464203681348</v>
       </c>
       <c r="I15" t="n">
-        <v>2.384938108663723</v>
+        <v>1.372163896230088</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726201560928138</v>
+        <v>4.68339968670168</v>
       </c>
       <c r="K15" t="n">
-        <v>16.25925387379172</v>
+        <v>17.62385373026366</v>
       </c>
       <c r="L15" t="n">
-        <v>43.58124803111146</v>
+        <v>42.27673175116133</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92057746156016</v>
+        <v>99.95428658552235</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>81.44249438552056</v>
+        <v>79.97489937739611</v>
       </c>
       <c r="C16" t="n">
-        <v>38.15111459814636</v>
+        <v>37.86527207657171</v>
       </c>
       <c r="D16" t="n">
-        <v>1.446548110619059</v>
+        <v>1.527014316509736</v>
       </c>
       <c r="E16" t="n">
-        <v>12.01803756231276</v>
+        <v>10.72237010543465</v>
       </c>
       <c r="F16" t="n">
-        <v>0.75680786473316</v>
+        <v>0.7497012539909129</v>
       </c>
       <c r="G16" t="n">
-        <v>23.96077982607415</v>
+        <v>24.88424141751997</v>
       </c>
       <c r="H16" t="n">
-        <v>36.54120546450989</v>
+        <v>36.26192430069342</v>
       </c>
       <c r="I16" t="n">
-        <v>1.989066402689294</v>
+        <v>1.144015145804213</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730049154582248</v>
+        <v>4.685632837443205</v>
       </c>
       <c r="K16" t="n">
-        <v>18.55750561447942</v>
+        <v>20.02510062260389</v>
       </c>
       <c r="L16" t="n">
-        <v>43.225131506578</v>
+        <v>42.07151163704023</v>
       </c>
       <c r="M16" t="n">
-        <v>99.9337517192038</v>
+        <v>99.96188433621583</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>83.02201844940622</v>
+        <v>84.55576361784284</v>
       </c>
       <c r="C17" t="n">
-        <v>39.31214430019385</v>
+        <v>40.8718383171701</v>
       </c>
       <c r="D17" t="n">
-        <v>1.447694477268464</v>
+        <v>1.527801797158861</v>
       </c>
       <c r="E17" t="n">
-        <v>12.75747899152058</v>
+        <v>12.33193925659478</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574076230749451</v>
+        <v>0.7500878746163777</v>
       </c>
       <c r="G17" t="n">
-        <v>24.38071746501272</v>
+        <v>26.2830869788534</v>
       </c>
       <c r="H17" t="n">
-        <v>36.97111289310243</v>
+        <v>37.66663732836658</v>
       </c>
       <c r="I17" t="n">
-        <v>1.973809355208685</v>
+        <v>1.308161165900491</v>
       </c>
       <c r="J17" t="n">
-        <v>4.733797644218405</v>
+        <v>4.68804921635236</v>
       </c>
       <c r="K17" t="n">
-        <v>16.97798155059377</v>
+        <v>15.44423638215715</v>
       </c>
       <c r="L17" t="n">
-        <v>43.64413260318103</v>
+        <v>43.64034240415772</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93425845396865</v>
+        <v>99.95641710348497</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.80144258707855</v>
+        <v>86.07557778635623</v>
       </c>
       <c r="C18" t="n">
-        <v>37.39686288277245</v>
+        <v>41.59119869106374</v>
       </c>
       <c r="D18" t="n">
-        <v>1.365307675146158</v>
+        <v>1.529022160212794</v>
       </c>
       <c r="E18" t="n">
-        <v>12.30579033060215</v>
+        <v>12.92227440570543</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7579219130411816</v>
+        <v>0.750687022706848</v>
       </c>
       <c r="G18" t="n">
-        <v>22.99323593701807</v>
+        <v>26.42243692633345</v>
       </c>
       <c r="H18" t="n">
-        <v>36.99621677616651</v>
+        <v>37.69672432829478</v>
       </c>
       <c r="I18" t="n">
-        <v>1.6459579985971</v>
+        <v>2.062639051185128</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737011956507382</v>
+        <v>4.6917938919178</v>
       </c>
       <c r="K18" t="n">
-        <v>19.19855741292146</v>
+        <v>13.92442221364379</v>
       </c>
       <c r="L18" t="n">
-        <v>43.3497516666614</v>
+        <v>44.41567933559655</v>
       </c>
       <c r="M18" t="n">
-        <v>99.9451719623553</v>
+        <v>99.93130024030407</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.88010181907404</v>
+        <v>83.38629593506703</v>
       </c>
       <c r="C19" t="n">
-        <v>36.72952036538598</v>
+        <v>39.22161630966725</v>
       </c>
       <c r="D19" t="n">
-        <v>1.331761018692021</v>
+        <v>1.429402507093236</v>
       </c>
       <c r="E19" t="n">
-        <v>12.23216382603419</v>
+        <v>12.36703023415621</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7583559740250831</v>
+        <v>0.751203181667351</v>
       </c>
       <c r="G19" t="n">
-        <v>22.42827449954172</v>
+        <v>24.70094846810965</v>
       </c>
       <c r="H19" t="n">
-        <v>37.01740446579282</v>
+        <v>37.72264392122113</v>
       </c>
       <c r="I19" t="n">
-        <v>1.372417197331446</v>
+        <v>1.720047737398497</v>
       </c>
       <c r="J19" t="n">
-        <v>4.739724837656767</v>
+        <v>4.695019885420944</v>
       </c>
       <c r="K19" t="n">
-        <v>20.11989818092596</v>
+        <v>16.61370406493299</v>
       </c>
       <c r="L19" t="n">
-        <v>43.10486039817147</v>
+        <v>44.10738409620018</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95427894448341</v>
+        <v>99.94270447080042</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>77.40366287006556</v>
+        <v>80.48153028017268</v>
       </c>
       <c r="C20" t="n">
-        <v>34.46472986891389</v>
+        <v>36.58271425521524</v>
       </c>
       <c r="D20" t="n">
-        <v>1.240740448948875</v>
+        <v>1.322333978997881</v>
       </c>
       <c r="E20" t="n">
-        <v>11.58685149745665</v>
+        <v>11.67972276038945</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7587296620672163</v>
+        <v>0.7516494099518626</v>
       </c>
       <c r="G20" t="n">
-        <v>20.89539112583482</v>
+        <v>22.85073890018477</v>
       </c>
       <c r="H20" t="n">
-        <v>37.03564518898018</v>
+        <v>37.7450518543809</v>
       </c>
       <c r="I20" t="n">
-        <v>1.144244558857705</v>
+        <v>1.434224564068661</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742060387920099</v>
+        <v>4.697808812199141</v>
       </c>
       <c r="K20" t="n">
-        <v>22.59633712993446</v>
+        <v>19.51846971982732</v>
       </c>
       <c r="L20" t="n">
-        <v>42.9008103012258</v>
+        <v>43.85103692114083</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96187730007414</v>
+        <v>99.95222089618339</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.910540997589</v>
+        <v>77.64958085250231</v>
       </c>
       <c r="C21" t="n">
-        <v>37.90569856144194</v>
+        <v>33.97169347797426</v>
       </c>
       <c r="D21" t="n">
-        <v>1.241536532754218</v>
+        <v>1.218510317422023</v>
       </c>
       <c r="E21" t="n">
-        <v>13.44036985437121</v>
+        <v>10.96198405764544</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7592164781431465</v>
+        <v>0.7520352557195327</v>
       </c>
       <c r="G21" t="n">
-        <v>22.48889674799412</v>
+        <v>21.05660260783221</v>
       </c>
       <c r="H21" t="n">
-        <v>38.63950671989114</v>
+        <v>37.76442760099319</v>
       </c>
       <c r="I21" t="n">
-        <v>1.595911676040507</v>
+        <v>1.195800664642848</v>
       </c>
       <c r="J21" t="n">
-        <v>4.745102988394663</v>
+        <v>4.700220348247079</v>
       </c>
       <c r="K21" t="n">
-        <v>17.08945900241099</v>
+        <v>22.35041914749767</v>
       </c>
       <c r="L21" t="n">
-        <v>44.95167949068463</v>
+        <v>43.63804780330393</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94683705453757</v>
+        <v>99.96016042877586</v>
       </c>
     </row>
   </sheetData>
